--- a/06_carteira-de-prospecao-comercial/C20_extensao-setor-imobiliario/NetWiz_Imobiliario_P2_Scorecard.xlsx
+++ b/06_carteira-de-prospecao-comercial/C20_extensao-setor-imobiliario/NetWiz_Imobiliario_P2_Scorecard.xlsx
@@ -324,7 +324,7 @@
     <t>Mapeamento bloqueio → serviço</t>
   </si>
   <si>
-    <t>Contraste com o anexo das grandes redes: aquelas davam média de 70,3 e zero casos de 'sem presença'. Estas independentes dão uma média muito inferior e vários casos de ausência de presença digital — é aqui que a oferta base da NetWiz (website e marketing) tem procura real. As pontuações são estimativas por observação pública e devem ser revalidadas com auditoria a cada site.</t>
+    <t>Estas agências independentes apresentam maturidade digital baixa, com vários casos de ausência de presença digital — é aqui que a oferta base da NetWiz (website e marketing) tem procura real. As pontuações são estimativas por observação pública e devem ser revalidadas com auditoria a cada site.</t>
   </si>
 </sst>
 </file>
